--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513370</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513357</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513354</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513356</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349822</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349827</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349828</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349824</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349829</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349841</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513353</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513368</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349825</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2467,6 +2557,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349826</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349833</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349838</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2770,6 +2875,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111349840</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114521872</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2986,8 +3101,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136288065</v>
       </c>
       <c r="B8" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136288076</v>
       </c>
       <c r="B9" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136288063</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136288093</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136288096</v>
       </c>
       <c r="B12" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>136292227</v>
       </c>
       <c r="B13" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136292230</v>
       </c>
       <c r="B14" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136288100</v>
       </c>
       <c r="B16" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>136288055</v>
       </c>
       <c r="B19" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136288077</v>
       </c>
       <c r="B20" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>136288103</v>
       </c>
       <c r="B23" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>136288087</v>
       </c>
       <c r="B24" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136288047</v>
       </c>
       <c r="B25" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136288056</v>
       </c>
       <c r="B26" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>136288062</v>
       </c>
       <c r="B27" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136288067</v>
       </c>
       <c r="B28" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136288069</v>
       </c>
       <c r="B29" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136288074</v>
       </c>
       <c r="B30" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136288079</v>
       </c>
       <c r="B31" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136288092</v>
       </c>
       <c r="B32" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136288095</v>
       </c>
       <c r="B33" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136288099</v>
       </c>
       <c r="B34" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136288107</v>
       </c>
       <c r="B35" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>136288112</v>
       </c>
       <c r="B36" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136288114</v>
       </c>
       <c r="B37" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>136292200</v>
       </c>
       <c r="B38" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>136292201</v>
       </c>
       <c r="B39" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136292231</v>
       </c>
       <c r="B40" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136292234</v>
       </c>
       <c r="B41" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136288046</v>
       </c>
       <c r="B46" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136288054</v>
       </c>
       <c r="B47" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136288057</v>
       </c>
       <c r="B48" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>136288058</v>
       </c>
       <c r="B49" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136288068</v>
       </c>
       <c r="B50" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>136288072</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>136288082</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>136288089</v>
       </c>
       <c r="B53" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136288094</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>136288098</v>
       </c>
       <c r="B55" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>136288102</v>
       </c>
       <c r="B56" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>136288105</v>
       </c>
       <c r="B57" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>136288110</v>
       </c>
       <c r="B58" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>136288117</v>
       </c>
       <c r="B59" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>136288118</v>
       </c>
       <c r="B60" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>136288119</v>
       </c>
       <c r="B61" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136288121</v>
       </c>
       <c r="B62" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>136288130</v>
       </c>
       <c r="B63" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136288131</v>
       </c>
       <c r="B64" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136288133</v>
       </c>
       <c r="B65" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>136288134</v>
       </c>
       <c r="B66" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136288136</v>
       </c>
       <c r="B67" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136292202</v>
       </c>
       <c r="B68" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>136292204</v>
       </c>
       <c r="B69" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>136292205</v>
       </c>
       <c r="B70" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>136292209</v>
       </c>
       <c r="B71" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>136292210</v>
       </c>
       <c r="B72" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>136292211</v>
       </c>
       <c r="B73" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136292212</v>
       </c>
       <c r="B74" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>136292214</v>
       </c>
       <c r="B75" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>136292218</v>
       </c>
       <c r="B76" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>136292219</v>
       </c>
       <c r="B77" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136292220</v>
       </c>
       <c r="B78" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>136292221</v>
       </c>
       <c r="B79" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>136292222</v>
       </c>
       <c r="B80" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>136292223</v>
       </c>
       <c r="B81" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136292224</v>
       </c>
       <c r="B82" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>136292225</v>
       </c>
       <c r="B83" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>136292229</v>
       </c>
       <c r="B84" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>136292233</v>
       </c>
       <c r="B85" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>136292236</v>
       </c>
       <c r="B86" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>136292237</v>
       </c>
       <c r="B87" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>136292238</v>
       </c>
       <c r="B88" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>136292239</v>
       </c>
       <c r="B89" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>136292243</v>
       </c>
       <c r="B90" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>136292245</v>
       </c>
       <c r="B91" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>136292249</v>
       </c>
       <c r="B92" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136292250</v>
       </c>
       <c r="B93" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136292254</v>
       </c>
       <c r="B94" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>136292256</v>
       </c>
       <c r="B95" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136292259</v>
       </c>
       <c r="B96" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>136292260</v>
       </c>
       <c r="B97" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>136292261</v>
       </c>
       <c r="B98" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>136288083</v>
       </c>
       <c r="B99" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136288108</v>
       </c>
       <c r="B100" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>136288109</v>
       </c>
       <c r="B101" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>136288116</v>
       </c>
       <c r="B102" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>136288085</v>
       </c>
       <c r="B104" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>136288088</v>
       </c>
       <c r="B105" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>136288086</v>
       </c>
       <c r="B111" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>136288123</v>
       </c>
       <c r="B112" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>136288125</v>
       </c>
       <c r="B113" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>136288129</v>
       </c>
       <c r="B114" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>136292252</v>
       </c>
       <c r="B115" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>136292228</v>
       </c>
       <c r="B116" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136288051</v>
       </c>
       <c r="B117" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>136288124</v>
       </c>
       <c r="B118" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>136288126</v>
       </c>
       <c r="B119" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>136292253</v>
       </c>
       <c r="B120" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136288049</v>
       </c>
       <c r="B122" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>136288073</v>
       </c>
       <c r="B123" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>136288078</v>
       </c>
       <c r="B124" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136292217</v>
       </c>
       <c r="B125" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>136292240</v>
       </c>
       <c r="B126" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>136292247</v>
       </c>
       <c r="B127" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>136288059</v>
       </c>
       <c r="B128" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>136288060</v>
       </c>
       <c r="B129" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>136288061</v>
       </c>
       <c r="B130" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>136288075</v>
       </c>
       <c r="B131" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>136288080</v>
       </c>
       <c r="B132" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>136288081</v>
       </c>
       <c r="B133" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136288084</v>
       </c>
       <c r="B134" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>136288090</v>
       </c>
       <c r="B135" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>136288104</v>
       </c>
       <c r="B136" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136288115</v>
       </c>
       <c r="B137" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>136288122</v>
       </c>
       <c r="B138" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>136292208</v>
       </c>
       <c r="B139" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>136292213</v>
       </c>
       <c r="B140" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>136292235</v>
       </c>
       <c r="B141" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>136288127</v>
       </c>
       <c r="B142" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>136288120</v>
       </c>
       <c r="B143" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>136292248</v>
       </c>
       <c r="B144" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>136288111</v>
       </c>
       <c r="B145" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>136288050</v>
       </c>
       <c r="B146" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>136288053</v>
       </c>
       <c r="B147" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>136288066</v>
       </c>
       <c r="B148" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>136288071</v>
       </c>
       <c r="B149" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>136288097</v>
       </c>
       <c r="B150" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>136288106</v>
       </c>
       <c r="B151" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>136292241</v>
       </c>
       <c r="B152" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>136288045</v>
       </c>
       <c r="B153" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>136288064</v>
       </c>
       <c r="B154" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>136288091</v>
       </c>
       <c r="B155" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>136288113</v>
       </c>
       <c r="B156" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>136292203</v>
       </c>
       <c r="B157" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>136292207</v>
       </c>
       <c r="B158" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>136292215</v>
       </c>
       <c r="B159" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>136292216</v>
       </c>
       <c r="B160" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>136292242</v>
       </c>
       <c r="B161" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>136292255</v>
       </c>
       <c r="B162" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>136292258</v>
       </c>
       <c r="B163" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>136288052</v>
       </c>
       <c r="B164" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136288065</v>
       </c>
       <c r="B8" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136288076</v>
       </c>
       <c r="B9" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136288063</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136288093</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136288096</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>136292227</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136292230</v>
       </c>
       <c r="B14" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136288100</v>
       </c>
       <c r="B16" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>136288055</v>
       </c>
       <c r="B19" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136288077</v>
       </c>
       <c r="B20" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>136288103</v>
       </c>
       <c r="B23" t="n">
-        <v>92267</v>
+        <v>92273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>136288087</v>
       </c>
       <c r="B24" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136288047</v>
       </c>
       <c r="B25" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136288056</v>
       </c>
       <c r="B26" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>136288062</v>
       </c>
       <c r="B27" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136288067</v>
       </c>
       <c r="B28" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136288069</v>
       </c>
       <c r="B29" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136288074</v>
       </c>
       <c r="B30" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136288079</v>
       </c>
       <c r="B31" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136288092</v>
       </c>
       <c r="B32" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136288095</v>
       </c>
       <c r="B33" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136288099</v>
       </c>
       <c r="B34" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136288107</v>
       </c>
       <c r="B35" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>136288112</v>
       </c>
       <c r="B36" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136288114</v>
       </c>
       <c r="B37" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>136292200</v>
       </c>
       <c r="B38" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>136292201</v>
       </c>
       <c r="B39" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136292231</v>
       </c>
       <c r="B40" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136292234</v>
       </c>
       <c r="B41" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136288046</v>
       </c>
       <c r="B46" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136288054</v>
       </c>
       <c r="B47" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136288057</v>
       </c>
       <c r="B48" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>136288058</v>
       </c>
       <c r="B49" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136288068</v>
       </c>
       <c r="B50" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>136288072</v>
       </c>
       <c r="B51" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>136288082</v>
       </c>
       <c r="B52" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>136288089</v>
       </c>
       <c r="B53" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136288094</v>
       </c>
       <c r="B54" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>136288098</v>
       </c>
       <c r="B55" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>136288102</v>
       </c>
       <c r="B56" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>136288105</v>
       </c>
       <c r="B57" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>136288110</v>
       </c>
       <c r="B58" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>136288117</v>
       </c>
       <c r="B59" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>136288118</v>
       </c>
       <c r="B60" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>136288119</v>
       </c>
       <c r="B61" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136288121</v>
       </c>
       <c r="B62" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>136288130</v>
       </c>
       <c r="B63" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136288131</v>
       </c>
       <c r="B64" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136288133</v>
       </c>
       <c r="B65" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>136288134</v>
       </c>
       <c r="B66" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136288136</v>
       </c>
       <c r="B67" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136292202</v>
       </c>
       <c r="B68" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>136292204</v>
       </c>
       <c r="B69" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>136292205</v>
       </c>
       <c r="B70" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>136292209</v>
       </c>
       <c r="B71" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>136292210</v>
       </c>
       <c r="B72" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>136292211</v>
       </c>
       <c r="B73" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136292212</v>
       </c>
       <c r="B74" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>136292214</v>
       </c>
       <c r="B75" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>136292218</v>
       </c>
       <c r="B76" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>136292219</v>
       </c>
       <c r="B77" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136292220</v>
       </c>
       <c r="B78" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>136292221</v>
       </c>
       <c r="B79" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>136292222</v>
       </c>
       <c r="B80" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>136292223</v>
       </c>
       <c r="B81" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136292224</v>
       </c>
       <c r="B82" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>136292225</v>
       </c>
       <c r="B83" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>136292229</v>
       </c>
       <c r="B84" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>136292233</v>
       </c>
       <c r="B85" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>136292236</v>
       </c>
       <c r="B86" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>136292237</v>
       </c>
       <c r="B87" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>136292238</v>
       </c>
       <c r="B88" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>136292239</v>
       </c>
       <c r="B89" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>136292243</v>
       </c>
       <c r="B90" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>136292245</v>
       </c>
       <c r="B91" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>136292249</v>
       </c>
       <c r="B92" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136292250</v>
       </c>
       <c r="B93" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136292254</v>
       </c>
       <c r="B94" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>136292256</v>
       </c>
       <c r="B95" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136292259</v>
       </c>
       <c r="B96" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>136292260</v>
       </c>
       <c r="B97" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>136292261</v>
       </c>
       <c r="B98" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>136288083</v>
       </c>
       <c r="B99" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136288108</v>
       </c>
       <c r="B100" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>136288109</v>
       </c>
       <c r="B101" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>136288116</v>
       </c>
       <c r="B102" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>136288085</v>
       </c>
       <c r="B104" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>136288088</v>
       </c>
       <c r="B105" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>136288086</v>
       </c>
       <c r="B111" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>136288123</v>
       </c>
       <c r="B112" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>136288125</v>
       </c>
       <c r="B113" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>136288129</v>
       </c>
       <c r="B114" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>136292252</v>
       </c>
       <c r="B115" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>136292228</v>
       </c>
       <c r="B116" t="n">
-        <v>80569</v>
+        <v>80573</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136288051</v>
       </c>
       <c r="B117" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>136288124</v>
       </c>
       <c r="B118" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>136288126</v>
       </c>
       <c r="B119" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>136292253</v>
       </c>
       <c r="B120" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>136288111</v>
       </c>
       <c r="B145" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>136288050</v>
       </c>
       <c r="B146" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>136288053</v>
       </c>
       <c r="B147" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>136288066</v>
       </c>
       <c r="B148" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>136288071</v>
       </c>
       <c r="B149" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>136288097</v>
       </c>
       <c r="B150" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>136288106</v>
       </c>
       <c r="B151" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>136292241</v>
       </c>
       <c r="B152" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>136288045</v>
       </c>
       <c r="B153" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>136288064</v>
       </c>
       <c r="B154" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>136288091</v>
       </c>
       <c r="B155" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>136288113</v>
       </c>
       <c r="B156" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>136292203</v>
       </c>
       <c r="B157" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>136292207</v>
       </c>
       <c r="B158" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>136292215</v>
       </c>
       <c r="B159" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>136292216</v>
       </c>
       <c r="B160" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>136292242</v>
       </c>
       <c r="B161" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>136292255</v>
       </c>
       <c r="B162" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>136292258</v>
       </c>
       <c r="B163" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>136288052</v>
       </c>
       <c r="B164" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136288065</v>
       </c>
       <c r="B8" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136288076</v>
       </c>
       <c r="B9" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136288063</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136288093</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136288096</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>136292227</v>
       </c>
       <c r="B13" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136292230</v>
       </c>
       <c r="B14" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136288100</v>
       </c>
       <c r="B16" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>136288055</v>
       </c>
       <c r="B19" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136288077</v>
       </c>
       <c r="B20" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>136288103</v>
       </c>
       <c r="B23" t="n">
-        <v>92273</v>
+        <v>92280</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>136288087</v>
       </c>
       <c r="B24" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136288047</v>
       </c>
       <c r="B25" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136288056</v>
       </c>
       <c r="B26" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>136288062</v>
       </c>
       <c r="B27" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136288067</v>
       </c>
       <c r="B28" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136288069</v>
       </c>
       <c r="B29" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136288074</v>
       </c>
       <c r="B30" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136288079</v>
       </c>
       <c r="B31" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136288092</v>
       </c>
       <c r="B32" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136288095</v>
       </c>
       <c r="B33" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136288099</v>
       </c>
       <c r="B34" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136288107</v>
       </c>
       <c r="B35" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>136288112</v>
       </c>
       <c r="B36" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136288114</v>
       </c>
       <c r="B37" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>136292200</v>
       </c>
       <c r="B38" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>136292201</v>
       </c>
       <c r="B39" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136292231</v>
       </c>
       <c r="B40" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136292234</v>
       </c>
       <c r="B41" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136288046</v>
       </c>
       <c r="B46" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136288054</v>
       </c>
       <c r="B47" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136288057</v>
       </c>
       <c r="B48" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>136288058</v>
       </c>
       <c r="B49" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136288068</v>
       </c>
       <c r="B50" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>136288072</v>
       </c>
       <c r="B51" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>136288082</v>
       </c>
       <c r="B52" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>136288089</v>
       </c>
       <c r="B53" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136288094</v>
       </c>
       <c r="B54" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>136288098</v>
       </c>
       <c r="B55" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>136288102</v>
       </c>
       <c r="B56" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>136288105</v>
       </c>
       <c r="B57" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>136288110</v>
       </c>
       <c r="B58" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>136288117</v>
       </c>
       <c r="B59" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>136288118</v>
       </c>
       <c r="B60" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>136288119</v>
       </c>
       <c r="B61" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136288121</v>
       </c>
       <c r="B62" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>136288130</v>
       </c>
       <c r="B63" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136288131</v>
       </c>
       <c r="B64" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136288133</v>
       </c>
       <c r="B65" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>136288134</v>
       </c>
       <c r="B66" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136288136</v>
       </c>
       <c r="B67" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136292202</v>
       </c>
       <c r="B68" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>136292204</v>
       </c>
       <c r="B69" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>136292205</v>
       </c>
       <c r="B70" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>136292209</v>
       </c>
       <c r="B71" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>136292210</v>
       </c>
       <c r="B72" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>136292211</v>
       </c>
       <c r="B73" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136292212</v>
       </c>
       <c r="B74" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>136292214</v>
       </c>
       <c r="B75" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>136292218</v>
       </c>
       <c r="B76" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>136292219</v>
       </c>
       <c r="B77" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136292220</v>
       </c>
       <c r="B78" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>136292221</v>
       </c>
       <c r="B79" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>136292222</v>
       </c>
       <c r="B80" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>136292223</v>
       </c>
       <c r="B81" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136292224</v>
       </c>
       <c r="B82" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>136292225</v>
       </c>
       <c r="B83" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>136292229</v>
       </c>
       <c r="B84" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>136292233</v>
       </c>
       <c r="B85" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>136292236</v>
       </c>
       <c r="B86" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>136292237</v>
       </c>
       <c r="B87" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>136292238</v>
       </c>
       <c r="B88" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>136292239</v>
       </c>
       <c r="B89" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>136292243</v>
       </c>
       <c r="B90" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>136292245</v>
       </c>
       <c r="B91" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>136292249</v>
       </c>
       <c r="B92" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136292250</v>
       </c>
       <c r="B93" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136292254</v>
       </c>
       <c r="B94" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>136292256</v>
       </c>
       <c r="B95" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136292259</v>
       </c>
       <c r="B96" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>136292260</v>
       </c>
       <c r="B97" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>136292261</v>
       </c>
       <c r="B98" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>136288083</v>
       </c>
       <c r="B99" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136288108</v>
       </c>
       <c r="B100" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>136288109</v>
       </c>
       <c r="B101" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>136288116</v>
       </c>
       <c r="B102" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>136288085</v>
       </c>
       <c r="B104" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>136288088</v>
       </c>
       <c r="B105" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>136288086</v>
       </c>
       <c r="B111" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>136288123</v>
       </c>
       <c r="B112" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>136288125</v>
       </c>
       <c r="B113" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>136288129</v>
       </c>
       <c r="B114" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>136292252</v>
       </c>
       <c r="B115" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>136292228</v>
       </c>
       <c r="B116" t="n">
-        <v>80573</v>
+        <v>80579</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136288051</v>
       </c>
       <c r="B117" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>136288124</v>
       </c>
       <c r="B118" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>136288126</v>
       </c>
       <c r="B119" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>136292253</v>
       </c>
       <c r="B120" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136288049</v>
       </c>
       <c r="B122" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>136288073</v>
       </c>
       <c r="B123" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>136288078</v>
       </c>
       <c r="B124" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136292217</v>
       </c>
       <c r="B125" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>136292240</v>
       </c>
       <c r="B126" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>136292247</v>
       </c>
       <c r="B127" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>136288059</v>
       </c>
       <c r="B128" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>136288060</v>
       </c>
       <c r="B129" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>136288061</v>
       </c>
       <c r="B130" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>136288075</v>
       </c>
       <c r="B131" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>136288080</v>
       </c>
       <c r="B132" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>136288081</v>
       </c>
       <c r="B133" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136288084</v>
       </c>
       <c r="B134" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>136288090</v>
       </c>
       <c r="B135" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>136288104</v>
       </c>
       <c r="B136" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136288115</v>
       </c>
       <c r="B137" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>136288122</v>
       </c>
       <c r="B138" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>136292208</v>
       </c>
       <c r="B139" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>136292213</v>
       </c>
       <c r="B140" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>136292235</v>
       </c>
       <c r="B141" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>136288127</v>
       </c>
       <c r="B142" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>136288120</v>
       </c>
       <c r="B143" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>136292248</v>
       </c>
       <c r="B144" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>136288111</v>
       </c>
       <c r="B145" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>136288050</v>
       </c>
       <c r="B146" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>136288053</v>
       </c>
       <c r="B147" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>136288066</v>
       </c>
       <c r="B148" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>136288071</v>
       </c>
       <c r="B149" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>136288097</v>
       </c>
       <c r="B150" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>136288106</v>
       </c>
       <c r="B151" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>136292241</v>
       </c>
       <c r="B152" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>136288045</v>
       </c>
       <c r="B153" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>136288064</v>
       </c>
       <c r="B154" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>136288091</v>
       </c>
       <c r="B155" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>136288113</v>
       </c>
       <c r="B156" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>136292203</v>
       </c>
       <c r="B157" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>136292207</v>
       </c>
       <c r="B158" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>136292215</v>
       </c>
       <c r="B159" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>136292216</v>
       </c>
       <c r="B160" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>136292242</v>
       </c>
       <c r="B161" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>136292255</v>
       </c>
       <c r="B162" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>136292258</v>
       </c>
       <c r="B163" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>136288052</v>
       </c>
       <c r="B164" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136288065</v>
       </c>
       <c r="B8" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136288076</v>
       </c>
       <c r="B9" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136288063</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136288093</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136288096</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>136292227</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136292230</v>
       </c>
       <c r="B14" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136288100</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>136288055</v>
       </c>
       <c r="B19" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136288077</v>
       </c>
       <c r="B20" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>136288103</v>
       </c>
       <c r="B23" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>136288087</v>
       </c>
       <c r="B24" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136288047</v>
       </c>
       <c r="B25" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136288056</v>
       </c>
       <c r="B26" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>136288062</v>
       </c>
       <c r="B27" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136288067</v>
       </c>
       <c r="B28" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136288069</v>
       </c>
       <c r="B29" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136288074</v>
       </c>
       <c r="B30" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136288079</v>
       </c>
       <c r="B31" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136288092</v>
       </c>
       <c r="B32" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136288095</v>
       </c>
       <c r="B33" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136288099</v>
       </c>
       <c r="B34" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136288107</v>
       </c>
       <c r="B35" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>136288112</v>
       </c>
       <c r="B36" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136288114</v>
       </c>
       <c r="B37" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>136292200</v>
       </c>
       <c r="B38" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>136292201</v>
       </c>
       <c r="B39" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136292231</v>
       </c>
       <c r="B40" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136292234</v>
       </c>
       <c r="B41" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>136288111</v>
       </c>
       <c r="B145" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>136288050</v>
       </c>
       <c r="B146" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>136288053</v>
       </c>
       <c r="B147" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>136288066</v>
       </c>
       <c r="B148" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>136288071</v>
       </c>
       <c r="B149" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>136288097</v>
       </c>
       <c r="B150" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>136288106</v>
       </c>
       <c r="B151" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>136292241</v>
       </c>
       <c r="B152" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>136288045</v>
       </c>
       <c r="B153" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>136288064</v>
       </c>
       <c r="B154" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>136288091</v>
       </c>
       <c r="B155" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>136288113</v>
       </c>
       <c r="B156" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>136292203</v>
       </c>
       <c r="B157" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>136292207</v>
       </c>
       <c r="B158" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>136292215</v>
       </c>
       <c r="B159" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>136292216</v>
       </c>
       <c r="B160" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>136292242</v>
       </c>
       <c r="B161" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>136292255</v>
       </c>
       <c r="B162" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>136292258</v>
       </c>
       <c r="B163" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>136288052</v>
       </c>
       <c r="B164" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136288065</v>
       </c>
       <c r="B8" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136288076</v>
       </c>
       <c r="B9" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136288063</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136288093</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136288096</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>136292227</v>
       </c>
       <c r="B13" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136292230</v>
       </c>
       <c r="B14" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136288100</v>
       </c>
       <c r="B16" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>136288055</v>
       </c>
       <c r="B19" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136288077</v>
       </c>
       <c r="B20" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>136288103</v>
       </c>
       <c r="B23" t="n">
-        <v>92281</v>
+        <v>92294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>136288087</v>
       </c>
       <c r="B24" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136288047</v>
       </c>
       <c r="B25" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136288056</v>
       </c>
       <c r="B26" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>136288062</v>
       </c>
       <c r="B27" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136288067</v>
       </c>
       <c r="B28" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136288069</v>
       </c>
       <c r="B29" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136288074</v>
       </c>
       <c r="B30" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136288079</v>
       </c>
       <c r="B31" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136288092</v>
       </c>
       <c r="B32" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136288095</v>
       </c>
       <c r="B33" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136288099</v>
       </c>
       <c r="B34" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136288107</v>
       </c>
       <c r="B35" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>136288112</v>
       </c>
       <c r="B36" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136288114</v>
       </c>
       <c r="B37" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>136292200</v>
       </c>
       <c r="B38" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>136292201</v>
       </c>
       <c r="B39" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136292231</v>
       </c>
       <c r="B40" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136292234</v>
       </c>
       <c r="B41" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136288046</v>
       </c>
       <c r="B46" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136288054</v>
       </c>
       <c r="B47" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136288057</v>
       </c>
       <c r="B48" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>136288058</v>
       </c>
       <c r="B49" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136288068</v>
       </c>
       <c r="B50" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>136288072</v>
       </c>
       <c r="B51" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>136288082</v>
       </c>
       <c r="B52" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>136288089</v>
       </c>
       <c r="B53" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136288094</v>
       </c>
       <c r="B54" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>136288098</v>
       </c>
       <c r="B55" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>136288102</v>
       </c>
       <c r="B56" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>136288105</v>
       </c>
       <c r="B57" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>136288110</v>
       </c>
       <c r="B58" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>136288117</v>
       </c>
       <c r="B59" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>136288118</v>
       </c>
       <c r="B60" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>136288119</v>
       </c>
       <c r="B61" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136288121</v>
       </c>
       <c r="B62" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>136288130</v>
       </c>
       <c r="B63" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136288131</v>
       </c>
       <c r="B64" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136288133</v>
       </c>
       <c r="B65" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>136288134</v>
       </c>
       <c r="B66" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136288136</v>
       </c>
       <c r="B67" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136292202</v>
       </c>
       <c r="B68" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>136292204</v>
       </c>
       <c r="B69" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>136292205</v>
       </c>
       <c r="B70" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>136292209</v>
       </c>
       <c r="B71" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>136292210</v>
       </c>
       <c r="B72" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>136292211</v>
       </c>
       <c r="B73" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136292212</v>
       </c>
       <c r="B74" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>136292214</v>
       </c>
       <c r="B75" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>136292218</v>
       </c>
       <c r="B76" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>136292219</v>
       </c>
       <c r="B77" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136292220</v>
       </c>
       <c r="B78" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>136292221</v>
       </c>
       <c r="B79" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>136292222</v>
       </c>
       <c r="B80" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>136292223</v>
       </c>
       <c r="B81" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136292224</v>
       </c>
       <c r="B82" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>136292225</v>
       </c>
       <c r="B83" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>136292229</v>
       </c>
       <c r="B84" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>136292233</v>
       </c>
       <c r="B85" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>136292236</v>
       </c>
       <c r="B86" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>136292237</v>
       </c>
       <c r="B87" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>136292238</v>
       </c>
       <c r="B88" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>136292239</v>
       </c>
       <c r="B89" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>136292243</v>
       </c>
       <c r="B90" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>136292245</v>
       </c>
       <c r="B91" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>136292249</v>
       </c>
       <c r="B92" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136292250</v>
       </c>
       <c r="B93" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136292254</v>
       </c>
       <c r="B94" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>136292256</v>
       </c>
       <c r="B95" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136292259</v>
       </c>
       <c r="B96" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>136292260</v>
       </c>
       <c r="B97" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>136292261</v>
       </c>
       <c r="B98" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>136288083</v>
       </c>
       <c r="B99" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136288108</v>
       </c>
       <c r="B100" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>136288109</v>
       </c>
       <c r="B101" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>136288116</v>
       </c>
       <c r="B102" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>136288085</v>
       </c>
       <c r="B104" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>136288088</v>
       </c>
       <c r="B105" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>136288086</v>
       </c>
       <c r="B111" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>136288123</v>
       </c>
       <c r="B112" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>136288125</v>
       </c>
       <c r="B113" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>136288129</v>
       </c>
       <c r="B114" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>136292252</v>
       </c>
       <c r="B115" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>136292228</v>
       </c>
       <c r="B116" t="n">
-        <v>80579</v>
+        <v>80592</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136288051</v>
       </c>
       <c r="B117" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>136288124</v>
       </c>
       <c r="B118" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>136288126</v>
       </c>
       <c r="B119" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>136292253</v>
       </c>
       <c r="B120" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136288049</v>
       </c>
       <c r="B122" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>136288073</v>
       </c>
       <c r="B123" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>136288078</v>
       </c>
       <c r="B124" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136292217</v>
       </c>
       <c r="B125" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>136292240</v>
       </c>
       <c r="B126" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>136292247</v>
       </c>
       <c r="B127" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>136288059</v>
       </c>
       <c r="B128" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>136288060</v>
       </c>
       <c r="B129" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>136288061</v>
       </c>
       <c r="B130" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>136288075</v>
       </c>
       <c r="B131" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>136288080</v>
       </c>
       <c r="B132" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>136288081</v>
       </c>
       <c r="B133" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136288084</v>
       </c>
       <c r="B134" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>136288090</v>
       </c>
       <c r="B135" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>136288104</v>
       </c>
       <c r="B136" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136288115</v>
       </c>
       <c r="B137" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>136288122</v>
       </c>
       <c r="B138" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>136292208</v>
       </c>
       <c r="B139" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>136292213</v>
       </c>
       <c r="B140" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>136292235</v>
       </c>
       <c r="B141" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>136288127</v>
       </c>
       <c r="B142" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>136288120</v>
       </c>
       <c r="B143" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>136292248</v>
       </c>
       <c r="B144" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>136288111</v>
       </c>
       <c r="B145" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>136288050</v>
       </c>
       <c r="B146" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>136288053</v>
       </c>
       <c r="B147" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>136288066</v>
       </c>
       <c r="B148" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>136288071</v>
       </c>
       <c r="B149" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>136288097</v>
       </c>
       <c r="B150" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>136288106</v>
       </c>
       <c r="B151" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>136292241</v>
       </c>
       <c r="B152" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>136288045</v>
       </c>
       <c r="B153" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>136288064</v>
       </c>
       <c r="B154" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>136288091</v>
       </c>
       <c r="B155" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>136288113</v>
       </c>
       <c r="B156" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>136292203</v>
       </c>
       <c r="B157" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>136292207</v>
       </c>
       <c r="B158" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>136292215</v>
       </c>
       <c r="B159" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>136292216</v>
       </c>
       <c r="B160" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>136292242</v>
       </c>
       <c r="B161" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>136292255</v>
       </c>
       <c r="B162" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>136292258</v>
       </c>
       <c r="B163" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>136288052</v>
       </c>
       <c r="B164" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 59005-2025 artfynd.xlsx
+++ b/artfynd/A 59005-2025 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>136288065</v>
       </c>
       <c r="B8" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136288076</v>
       </c>
       <c r="B9" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136288063</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136288093</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136288096</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>136292227</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>136292230</v>
       </c>
       <c r="B14" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136288100</v>
       </c>
       <c r="B16" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>136288055</v>
       </c>
       <c r="B19" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136288077</v>
       </c>
       <c r="B20" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>136288103</v>
       </c>
       <c r="B23" t="n">
-        <v>92294</v>
+        <v>92295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>136288087</v>
       </c>
       <c r="B24" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136288047</v>
       </c>
       <c r="B25" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136288056</v>
       </c>
       <c r="B26" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>136288062</v>
       </c>
       <c r="B27" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>136288067</v>
       </c>
       <c r="B28" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>136288069</v>
       </c>
       <c r="B29" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136288074</v>
       </c>
       <c r="B30" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136288079</v>
       </c>
       <c r="B31" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136288092</v>
       </c>
       <c r="B32" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136288095</v>
       </c>
       <c r="B33" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136288099</v>
       </c>
       <c r="B34" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136288107</v>
       </c>
       <c r="B35" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>136288112</v>
       </c>
       <c r="B36" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136288114</v>
       </c>
       <c r="B37" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>136292200</v>
       </c>
       <c r="B38" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>136292201</v>
       </c>
       <c r="B39" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136292231</v>
       </c>
       <c r="B40" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136292234</v>
       </c>
       <c r="B41" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136288046</v>
       </c>
       <c r="B46" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136288054</v>
       </c>
       <c r="B47" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136288057</v>
       </c>
       <c r="B48" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>136288058</v>
       </c>
       <c r="B49" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136288068</v>
       </c>
       <c r="B50" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>136288072</v>
       </c>
       <c r="B51" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>136288082</v>
       </c>
       <c r="B52" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>136288089</v>
       </c>
       <c r="B53" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>136288094</v>
       </c>
       <c r="B54" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>136288098</v>
       </c>
       <c r="B55" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>136288102</v>
       </c>
       <c r="B56" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>136288105</v>
       </c>
       <c r="B57" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>136288110</v>
       </c>
       <c r="B58" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>136288117</v>
       </c>
       <c r="B59" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>136288118</v>
       </c>
       <c r="B60" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>136288119</v>
       </c>
       <c r="B61" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136288121</v>
       </c>
       <c r="B62" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>136288130</v>
       </c>
       <c r="B63" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>136288131</v>
       </c>
       <c r="B64" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136288133</v>
       </c>
       <c r="B65" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>136288134</v>
       </c>
       <c r="B66" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>136288136</v>
       </c>
       <c r="B67" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136292202</v>
       </c>
       <c r="B68" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>136292204</v>
       </c>
       <c r="B69" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>136292205</v>
       </c>
       <c r="B70" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>136292209</v>
       </c>
       <c r="B71" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>136292210</v>
       </c>
       <c r="B72" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>136292211</v>
       </c>
       <c r="B73" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>136292212</v>
       </c>
       <c r="B74" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>136292214</v>
       </c>
       <c r="B75" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>136292218</v>
       </c>
       <c r="B76" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>136292219</v>
       </c>
       <c r="B77" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136292220</v>
       </c>
       <c r="B78" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>136292221</v>
       </c>
       <c r="B79" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>136292222</v>
       </c>
       <c r="B80" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>136292223</v>
       </c>
       <c r="B81" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136292224</v>
       </c>
       <c r="B82" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>136292225</v>
       </c>
       <c r="B83" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>136292229</v>
       </c>
       <c r="B84" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>136292233</v>
       </c>
       <c r="B85" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>136292236</v>
       </c>
       <c r="B86" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>136292237</v>
       </c>
       <c r="B87" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>136292238</v>
       </c>
       <c r="B88" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>136292239</v>
       </c>
       <c r="B89" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>136292243</v>
       </c>
       <c r="B90" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>136292245</v>
       </c>
       <c r="B91" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>136292249</v>
       </c>
       <c r="B92" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136292250</v>
       </c>
       <c r="B93" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136292254</v>
       </c>
       <c r="B94" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>136292256</v>
       </c>
       <c r="B95" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>136292259</v>
       </c>
       <c r="B96" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>136292260</v>
       </c>
       <c r="B97" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>136292261</v>
       </c>
       <c r="B98" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>136288083</v>
       </c>
       <c r="B99" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>136288108</v>
       </c>
       <c r="B100" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>136288109</v>
       </c>
       <c r="B101" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>136288116</v>
       </c>
       <c r="B102" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>136288085</v>
       </c>
       <c r="B104" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>136288088</v>
       </c>
       <c r="B105" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>136288086</v>
       </c>
       <c r="B111" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>136288123</v>
       </c>
       <c r="B112" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>136288125</v>
       </c>
       <c r="B113" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>136288129</v>
       </c>
       <c r="B114" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>136292252</v>
       </c>
       <c r="B115" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>136292228</v>
       </c>
       <c r="B116" t="n">
-        <v>80592</v>
+        <v>80593</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136288051</v>
       </c>
       <c r="B117" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>136288124</v>
       </c>
       <c r="B118" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>136288126</v>
       </c>
       <c r="B119" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>136292253</v>
       </c>
       <c r="B120" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>136288111</v>
       </c>
       <c r="B145" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>136288050</v>
       </c>
       <c r="B146" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>136288053</v>
       </c>
       <c r="B147" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>136288066</v>
       </c>
       <c r="B148" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>136288071</v>
       </c>
       <c r="B149" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>136288097</v>
       </c>
       <c r="B150" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>136288106</v>
       </c>
       <c r="B151" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>136292241</v>
       </c>
       <c r="B152" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>136288045</v>
       </c>
       <c r="B153" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>136288064</v>
       </c>
       <c r="B154" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>136288091</v>
       </c>
       <c r="B155" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>136288113</v>
       </c>
       <c r="B156" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>136292203</v>
       </c>
       <c r="B157" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>136292207</v>
       </c>
       <c r="B158" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>136292215</v>
       </c>
       <c r="B159" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>136292216</v>
       </c>
       <c r="B160" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>136292242</v>
       </c>
       <c r="B161" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>136292255</v>
       </c>
       <c r="B162" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>136292258</v>
       </c>
       <c r="B163" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>136288052</v>
       </c>
       <c r="B164" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
